--- a/Excel/NAME.xlsx
+++ b/Excel/NAME.xlsx
@@ -400,7 +400,7 @@
   <sheetPr>
     <tabColor/>
   </sheetPr>
-  <dimension ref="B11"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="13" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="16.1836" customWidth="1"/>
@@ -440,58 +440,291 @@
       </c>
     </row>
     <row r="4" spans="2:3">
-      <c r="B4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" t="s">
-        <v>8</v>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>布朗</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>安诺</t>
+        </is>
       </c>
     </row>
     <row r="5" spans="2:3">
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" t="s">
-        <v>9</v>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>福德</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>恩佐</t>
+        </is>
       </c>
     </row>
     <row r="6" spans="2:3">
-      <c r="B6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" t="s">
-        <v>10</v>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>莫尔</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>尔登</t>
+        </is>
       </c>
     </row>
     <row r="7" spans="2:3">
-      <c r="B7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" t="s">
-        <v>11</v>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>凯恩</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>吉安</t>
+        </is>
       </c>
     </row>
     <row r="8" spans="2:3">
-      <c r="B8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" t="s">
-        <v>12</v>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>格林</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>柯尔</t>
+        </is>
       </c>
     </row>
     <row r="9" spans="2:2">
-      <c r="B9" t="s">
-        <v>17</v>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>沃德</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>米洛</t>
+        </is>
       </c>
     </row>
     <row r="10" spans="2:2">
-      <c r="B10" t="s">
-        <v>18</v>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>里德</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>瑞安</t>
+        </is>
       </c>
     </row>
     <row r="11" spans="2:2">
-      <c r="B11" t="s">
-        <v>19</v>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>费恩</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>希洛</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" spans="2:2">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>塔伦</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>亚林</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" spans="2:2">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>兰德</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>尤恩</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" spans="2:2">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>贝克</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>霍安</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" spans="2:2">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>赫尔</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>缪尔</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" spans="2:2">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>德恩</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>蒂恩</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" spans="2:2">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>奥斯</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>芙洛</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" spans="2:2">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>韦尔</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>妮尔</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" spans="2:2">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>伊文</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>丝维</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" spans="2:2">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>佩恩</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>薇洛</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" spans="2:2">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>萨恩</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>琳恩</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" spans="2:2">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>诺德</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>琪安</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" spans="2:2">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>艾恩</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>多洛</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" spans="2:2">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>卡恩</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>桑诺</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" spans="2:2">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>罗恩</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>陶林</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" spans="2:2">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>加尔</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>温特</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" spans="2:2">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>泽恩</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>佐伊</t>
+        </is>
       </c>
     </row>
   </sheetData>
